--- a/business_forms/032_risk_manager_information_form--business_forms.xlsx
+++ b/business_forms/032_risk_manager_information_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,82 +548,82 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>What is your risk level?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>risk_manager</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk Manager</t>
+          <t>Describe the risk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>risk_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What is the risk type?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>risk_type</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk Type</t>
+          <t>How often does this risk occur?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,453 +635,108 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>How severe is this risk?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>risk_manager_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mitigation</t>
+          <t>risk_manager_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mitigation</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_manager_email</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk Manager's Email</t>
+          <t>What is your status for this risk?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>risk_manager_phone</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk Manager's Phone</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>risk_level_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>risk_level</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>risk_status</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>risk_status_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Risk Status</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>risk_status_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>risk_status_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Risk Status</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>risk_status_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>risk_status_5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Risk Status</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>risk_status_6</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>risk_status_7</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Risk Status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>risk_status_8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>risk_status_9</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>risk_status_10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>risk_status_11</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Risk Status</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>risk_status_12</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1466,661 +1121,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>risk_level_2_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>open</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>risk_level_2_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>risk_level_2_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>risk_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>risk_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>risk_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>risk_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>risk_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>risk_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>risk_status_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>risk_status_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>risk_status_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>risk_status_4_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>risk_status_4_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>risk_status_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>risk_status_5_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>risk_status_5_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>risk_status_5_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>risk_status_6_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>risk_status_6_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>risk_status_6_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>risk_status_7_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>risk_status_7_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>risk_status_7_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>risk_status_8_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>risk_status_8_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>risk_status_8_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>risk_status_9_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>risk_status_9_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>risk_status_9_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>risk_status_10_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>risk_status_10_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>risk_status_10_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>risk_status_11_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>risk_status_11_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>risk_status_11_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>risk_status_12_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>risk_status_12_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>risk_status_12_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
